--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260714.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260714.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.85%</t>
+          <t>10.96%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>8.76%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>7.39%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.30%</t>
+          <t>7.11%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>5.86%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>5.47%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>5.41%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>4.95%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,417,000</t>
+          <t>9,519,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.65%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>9,231,000</t>
+          <t>2,417,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.49%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.17%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>15,139,000</t>
+          <t>15,284,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>5,052,000</t>
+          <t>5,181,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>3.64%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>411,000</t>
+          <t>3,528,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,528,000</t>
+          <t>349,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1166,24 +1166,24 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2,966,000</t>
+          <t>528,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>528,000</t>
+          <t>2,966,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,508,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,22 +1283,22 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>1,508,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>50,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,703,284,932</t>
+          <t>3,212,985,822</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-3,322,852,533</t>
+          <t>-1,418,320,925</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
